--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -618,31 +618,31 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>0.5025559999999998</v>
+        <v>0.5035359999999998</v>
       </c>
       <c r="D2">
-        <v>0.4879279999999993</v>
+        <v>0.4889879999999993</v>
       </c>
       <c r="E2">
-        <v>0.4850537176443364</v>
+        <v>0.4880998606769701</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.4962370216909646</v>
+        <v>0.4972515799535244</v>
       </c>
       <c r="H2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="I2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5206818961625282</v>
+        <v>0.5235678365171035</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -665,31 +665,31 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>0.4686639999999987</v>
+        <v>0.4674799999999988</v>
       </c>
       <c r="D3">
-        <v>0.4831359999999993</v>
+        <v>0.4820999999999993</v>
       </c>
       <c r="E3">
-        <v>0.4848653204771308</v>
+        <v>0.4816348617949026</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4749155896970425</v>
+        <v>0.473795522482778</v>
       </c>
       <c r="H3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="I3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4501181038374718</v>
+        <v>0.4472321634828965</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -712,25 +712,25 @@
         <v>58</v>
       </c>
       <c r="C4">
-        <v>1.128</v>
+        <v>1.076</v>
       </c>
       <c r="D4">
-        <v>1.252</v>
+        <v>1.236</v>
       </c>
       <c r="E4">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="F4">
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="L4">
         <v>0.8200692764238203</v>
@@ -753,25 +753,25 @@
         <v>58</v>
       </c>
       <c r="C5">
-        <v>1.412</v>
+        <v>1.344</v>
       </c>
       <c r="D5">
-        <v>1.808</v>
+        <v>1.788</v>
       </c>
       <c r="E5">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F5">
         <v>2.2</v>
       </c>
       <c r="G5">
-        <v>1.603126377165344</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1.699906626866217</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L5">
         <v>1.746417103282563</v>
@@ -794,25 +794,25 @@
         <v>58</v>
       </c>
       <c r="C6">
-        <v>7.968</v>
+        <v>7.772</v>
       </c>
       <c r="D6">
-        <v>8.868</v>
+        <v>8.804</v>
       </c>
       <c r="E6">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="F6">
         <v>9.4</v>
       </c>
       <c r="G6">
-        <v>8.402378129921239</v>
+        <v>8.270086922309687</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>10.0582691946606</v>
+        <v>9.770258645592461</v>
       </c>
       <c r="L6">
         <v>4.467028425282805</v>
@@ -835,25 +835,25 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="D7">
-        <v>4.812</v>
+        <v>4.696</v>
       </c>
       <c r="E7">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>4.153921090288683</v>
+        <v>4.046198812423416</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>5.586198698614951</v>
+        <v>5.170440884727479</v>
       </c>
       <c r="L7">
         <v>2.262338789582505</v>
@@ -876,25 +876,25 @@
         <v>58</v>
       </c>
       <c r="C8">
-        <v>13.58</v>
+        <v>13.548</v>
       </c>
       <c r="D8">
-        <v>14.788</v>
+        <v>14.728</v>
       </c>
       <c r="E8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.16303197882762</v>
+        <v>14.1175179925634</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>19.01148659179185</v>
+        <v>18.83927196478475</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -917,25 +917,25 @@
         <v>58</v>
       </c>
       <c r="C9">
-        <v>3.184</v>
+        <v>2.824</v>
       </c>
       <c r="D9">
-        <v>4.004</v>
+        <v>3.956</v>
       </c>
       <c r="E9">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="F9">
         <v>5.8</v>
       </c>
       <c r="G9">
-        <v>3.579766740594905</v>
+        <v>3.370351158967601</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>1.550377686812013</v>
+        <v>0.8437214709471421</v>
       </c>
       <c r="L9">
         <v>7.059923274159115</v>
@@ -958,25 +958,25 @@
         <v>58</v>
       </c>
       <c r="C10">
-        <v>172.984</v>
+        <v>173.496</v>
       </c>
       <c r="D10">
-        <v>170.488</v>
+        <v>170.784</v>
       </c>
       <c r="E10">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="F10">
         <v>169.2</v>
       </c>
       <c r="G10">
-        <v>171.7793246530184</v>
+        <v>172.1870739018374</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>172.6467820636017</v>
+        <v>173.6497555759981</v>
       </c>
       <c r="L10">
         <v>4.764861070548267</v>
@@ -999,25 +999,25 @@
         <v>58</v>
       </c>
       <c r="C11">
-        <v>3.948</v>
+        <v>3.444</v>
       </c>
       <c r="D11">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="E11">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="F11">
         <v>7.4</v>
       </c>
       <c r="G11">
-        <v>4.417128380314937</v>
+        <v>4.127421591076081</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>1.16567981478854</v>
+        <v>0.2404700937671027</v>
       </c>
       <c r="L11">
         <v>9.933150479214353</v>
@@ -1040,25 +1040,25 @@
         <v>58</v>
       </c>
       <c r="C12">
-        <v>3.692</v>
+        <v>3.784</v>
       </c>
       <c r="D12">
-        <v>3.192</v>
+        <v>3.252</v>
       </c>
       <c r="E12">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.450678816710424</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.475459163737268</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L12">
         <v>0.887818750560327</v>
@@ -1081,25 +1081,25 @@
         <v>58</v>
       </c>
       <c r="C13">
-        <v>1.832</v>
+        <v>1.904</v>
       </c>
       <c r="D13">
-        <v>1.772</v>
+        <v>1.796</v>
       </c>
       <c r="E13">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="F13">
         <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.803041458005251</v>
+        <v>1.851874624409452</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>2.554644495322226</v>
+        <v>2.604250820161925</v>
       </c>
       <c r="L13">
         <v>1.198624596172324</v>
@@ -1122,25 +1122,25 @@
         <v>58</v>
       </c>
       <c r="C14">
-        <v>13.316</v>
+        <v>13.532</v>
       </c>
       <c r="D14">
-        <v>12.472</v>
+        <v>12.556</v>
       </c>
       <c r="E14">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F14">
         <v>11.8</v>
       </c>
       <c r="G14">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L14">
         <v>3.125306797245826</v>
@@ -1163,25 +1163,25 @@
         <v>58</v>
       </c>
       <c r="C15">
-        <v>8.612</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="D15">
-        <v>6.564</v>
+        <v>6.752</v>
       </c>
       <c r="E15">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="F15">
         <v>6.6</v>
       </c>
       <c r="G15">
-        <v>7.623548433245896</v>
+        <v>7.792923558442745</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>3.808811132083866</v>
+        <v>4.301787319744047</v>
       </c>
       <c r="L15">
         <v>4.673523904256721</v>
@@ -1204,25 +1204,25 @@
         <v>58</v>
       </c>
       <c r="C16">
-        <v>15.048</v>
+        <v>15.328</v>
       </c>
       <c r="D16">
-        <v>14.824</v>
+        <v>14.864</v>
       </c>
       <c r="E16">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="F16">
         <v>14.2</v>
       </c>
       <c r="G16">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="L16">
         <v>6.129350049043507</v>
@@ -1245,25 +1245,25 @@
         <v>58</v>
       </c>
       <c r="C17">
-        <v>7.352</v>
+        <v>7.492</v>
       </c>
       <c r="D17">
-        <v>5.764</v>
+        <v>5.94</v>
       </c>
       <c r="E17">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="F17">
         <v>5.8</v>
       </c>
       <c r="G17">
-        <v>6.585563921872306</v>
+        <v>6.742939047069155</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.801946011202828</v>
+        <v>5.212253933741241</v>
       </c>
       <c r="L17">
         <v>3.997862832988686</v>
@@ -1286,25 +1286,25 @@
         <v>58</v>
       </c>
       <c r="C18">
-        <v>172.1</v>
+        <v>171.868</v>
       </c>
       <c r="D18">
-        <v>175.156</v>
+        <v>174.552</v>
       </c>
       <c r="E18">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F18">
         <v>172.6</v>
       </c>
       <c r="G18">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L18">
         <v>24.70132137894479</v>
@@ -1327,25 +1327,25 @@
         <v>58</v>
       </c>
       <c r="C19">
-        <v>5.304</v>
+        <v>5.384</v>
       </c>
       <c r="D19">
-        <v>4.316</v>
+        <v>4.436</v>
       </c>
       <c r="E19">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F19">
         <v>4.4</v>
       </c>
       <c r="G19">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
       </c>
       <c r="K19">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L19">
         <v>2.858585552684069</v>
@@ -1368,25 +1368,25 @@
         <v>59</v>
       </c>
       <c r="C20">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="D20">
-        <v>0.512</v>
+        <v>0.496</v>
       </c>
       <c r="E20">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="F20">
         <v>0.4</v>
       </c>
       <c r="G20">
-        <v>0.4356836106718179</v>
+        <v>0.4345229085967423</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
       </c>
       <c r="K20">
-        <v>0.8003007397713651</v>
+        <v>0.7868170324027036</v>
       </c>
       <c r="L20">
         <v>0.8079772006265793</v>
@@ -1409,19 +1409,19 @@
         <v>59</v>
       </c>
       <c r="C21">
-        <v>0.236</v>
+        <v>0.244</v>
       </c>
       <c r="D21">
-        <v>0.184</v>
+        <v>0.188</v>
       </c>
       <c r="E21">
-        <v>-0.05756181698960205</v>
+        <v>-0.06175632720386842</v>
       </c>
       <c r="F21">
         <v>0.2</v>
       </c>
       <c r="G21">
-        <v>0.2115586961462879</v>
+        <v>0.2176785958498485</v>
       </c>
       <c r="J21" t="s">
         <v>4</v>
@@ -1450,25 +1450,25 @@
         <v>59</v>
       </c>
       <c r="C22">
-        <v>1.164</v>
+        <v>1.168</v>
       </c>
       <c r="D22">
-        <v>1.34</v>
+        <v>1.328</v>
       </c>
       <c r="E22">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="F22">
         <v>1.4</v>
       </c>
       <c r="G22">
-        <v>1.246724413043333</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="J22" t="s">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>1.234402433809649</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="L22">
         <v>0.9319718387197466</v>
@@ -1491,25 +1491,25 @@
         <v>59</v>
       </c>
       <c r="C23">
-        <v>0.612</v>
+        <v>0.6</v>
       </c>
       <c r="D23">
-        <v>0.732</v>
+        <v>0.696</v>
       </c>
       <c r="E23">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F23">
         <v>0.6</v>
       </c>
       <c r="G23">
-        <v>0.6684030088931816</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J23" t="s">
         <v>4</v>
       </c>
       <c r="K23">
-        <v>0.3293773794100608</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L23">
         <v>1.559831022862906</v>
@@ -1532,25 +1532,25 @@
         <v>59</v>
       </c>
       <c r="C24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="D24">
-        <v>1.54</v>
+        <v>1.584</v>
       </c>
       <c r="E24">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="F24">
         <v>1.6</v>
       </c>
       <c r="G24">
-        <v>1.730790973320455</v>
+        <v>1.762071575099091</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>1.430889012604439</v>
+        <v>1.52157415011752</v>
       </c>
       <c r="L24">
         <v>1.157976831184469</v>
@@ -1573,19 +1573,19 @@
         <v>59</v>
       </c>
       <c r="C25">
-        <v>0.676</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D25">
-        <v>0.612</v>
+        <v>0.608</v>
       </c>
       <c r="E25">
-        <v>-0.005331174175850051</v>
+        <v>-0.01550360442781762</v>
       </c>
       <c r="F25">
         <v>0.6</v>
       </c>
       <c r="G25">
-        <v>0.6459183952569697</v>
+        <v>0.6503979940712121</v>
       </c>
       <c r="J25" t="s">
         <v>4</v>
@@ -1614,25 +1614,25 @@
         <v>59</v>
       </c>
       <c r="C26">
-        <v>13.232</v>
+        <v>13.288</v>
       </c>
       <c r="D26">
-        <v>12.328</v>
+        <v>12.416</v>
       </c>
       <c r="E26">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="F26">
         <v>12.4</v>
       </c>
       <c r="G26">
-        <v>12.8070973330047</v>
+        <v>12.87813813537621</v>
       </c>
       <c r="J26" t="s">
         <v>4</v>
       </c>
       <c r="K26">
-        <v>11.23658004704028</v>
+        <v>11.45044534583586</v>
       </c>
       <c r="L26">
         <v>2.351026032651849</v>
@@ -1655,25 +1655,25 @@
         <v>59</v>
       </c>
       <c r="C27">
-        <v>1.736</v>
+        <v>1.604</v>
       </c>
       <c r="D27">
-        <v>1.98</v>
+        <v>1.924</v>
       </c>
       <c r="E27">
-        <v>0.06755162617559574</v>
+        <v>-0.1313628720128142</v>
       </c>
       <c r="F27">
         <v>2.4</v>
       </c>
       <c r="G27">
-        <v>1.850686118082802</v>
+        <v>1.754408023715151</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>0.06755162617559574</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>1.736334852416627</v>
@@ -1696,25 +1696,25 @@
         <v>59</v>
       </c>
       <c r="C28">
-        <v>0.164</v>
+        <v>0.18</v>
       </c>
       <c r="D28">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="E28">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="F28">
         <v>0.2</v>
       </c>
       <c r="G28">
-        <v>0.2128826077074241</v>
+        <v>0.2194821062252271</v>
       </c>
       <c r="J28" t="s">
         <v>4</v>
       </c>
       <c r="K28">
-        <v>0.6905082799680116</v>
+        <v>0.6788079824227848</v>
       </c>
       <c r="L28">
         <v>0.4925498319332764</v>
@@ -1740,22 +1740,22 @@
         <v>0.632</v>
       </c>
       <c r="D29">
-        <v>0.416</v>
+        <v>0.44</v>
       </c>
       <c r="E29">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F29">
         <v>0.4</v>
       </c>
       <c r="G29">
-        <v>0.530474583992273</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J29" t="s">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L29">
         <v>0.7620693762924241</v>
@@ -1819,25 +1819,25 @@
         <v>59</v>
       </c>
       <c r="C31">
-        <v>0.716</v>
+        <v>0.74</v>
       </c>
       <c r="D31">
-        <v>0.66</v>
+        <v>0.672</v>
       </c>
       <c r="E31">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="F31">
         <v>0.6</v>
       </c>
       <c r="G31">
-        <v>0.6896785958498485</v>
+        <v>0.7080382949605304</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31">
-        <v>0.9608490161719081</v>
+        <v>0.9935995824715044</v>
       </c>
       <c r="L31">
         <v>0.3332002265469857</v>
@@ -1860,25 +1860,25 @@
         <v>59</v>
       </c>
       <c r="C32">
-        <v>1.084</v>
+        <v>1.12</v>
       </c>
       <c r="D32">
-        <v>1.172</v>
+        <v>1.168</v>
       </c>
       <c r="E32">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>1.125362206521666</v>
+        <v>1.142561203557273</v>
       </c>
       <c r="J32" t="s">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>1.761149755943273</v>
+        <v>1.780416614874208</v>
       </c>
       <c r="L32">
         <v>0.8500971208676269</v>
@@ -1901,25 +1901,25 @@
         <v>59</v>
       </c>
       <c r="C33">
-        <v>0.552</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D33">
-        <v>0.392</v>
+        <v>0.408</v>
       </c>
       <c r="E33">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="F33">
         <v>0.4</v>
       </c>
       <c r="G33">
-        <v>0.4767959881424244</v>
+        <v>0.4885561887353032</v>
       </c>
       <c r="J33" t="s">
         <v>4</v>
       </c>
       <c r="K33">
-        <v>0.2703407362038964</v>
+        <v>0.3147916000487194</v>
       </c>
       <c r="L33">
         <v>0.3921195507989373</v>
@@ -1942,25 +1942,25 @@
         <v>59</v>
       </c>
       <c r="C34">
-        <v>10.028</v>
+        <v>9.932</v>
       </c>
       <c r="D34">
-        <v>11.468</v>
+        <v>11.352</v>
       </c>
       <c r="E34">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="F34">
         <v>11.6</v>
       </c>
       <c r="G34">
-        <v>10.70483610671818</v>
+        <v>10.59943560523598</v>
       </c>
       <c r="J34" t="s">
         <v>4</v>
       </c>
       <c r="K34">
-        <v>13.28203815275881</v>
+        <v>12.86475247157808</v>
       </c>
       <c r="L34">
         <v>3.050242274051084</v>
@@ -1986,22 +1986,22 @@
         <v>0.632</v>
       </c>
       <c r="D35">
-        <v>0.416</v>
+        <v>0.44</v>
       </c>
       <c r="E35">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="F35">
         <v>0.4</v>
       </c>
       <c r="G35">
-        <v>0.530474583992273</v>
+        <v>0.5417551857709093</v>
       </c>
       <c r="J35" t="s">
         <v>4</v>
       </c>
       <c r="K35">
-        <v>0.6558051063869967</v>
+        <v>0.7530958545051754</v>
       </c>
       <c r="L35">
         <v>0.7620693762924241</v>

--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -519,28 +519,28 @@
         <v>0.5141399999999998</v>
       </c>
       <c r="D2">
-        <v>0.4962479999999996</v>
+        <v>0.4961759999999997</v>
       </c>
       <c r="E2">
-        <v>0.496420004125868</v>
+        <v>0.4965980195557412</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064233115088753</v>
+        <v>0.5063922584364764</v>
       </c>
       <c r="H2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="I2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5278010224494333</v>
+        <v>0.5277257599289993</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -566,28 +566,28 @@
         <v>0.4579319999999985</v>
       </c>
       <c r="D3">
-        <v>0.4751159999999989</v>
+        <v>0.4751759999999988</v>
       </c>
       <c r="E3">
-        <v>0.4730562578730623</v>
+        <v>0.4728409805834767</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4653433332792005</v>
+        <v>0.4653692108395329</v>
       </c>
       <c r="H3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="I3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4429989775505667</v>
+        <v>0.4430742400710007</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>

--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -516,31 +516,31 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>0.5141399999999998</v>
+        <v>0.5143399999999999</v>
       </c>
       <c r="D2">
-        <v>0.4961759999999997</v>
+        <v>0.4959839999999996</v>
       </c>
       <c r="E2">
-        <v>0.4965980195557412</v>
+        <v>0.4965387457485618</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5063922584364764</v>
+        <v>0.5064231917089714</v>
       </c>
       <c r="H2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="I2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5277257599289993</v>
+        <v>0.5264302802913263</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -563,31 +563,31 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.4579319999999985</v>
+        <v>0.4577039999999986</v>
       </c>
       <c r="D3">
-        <v>0.4751759999999988</v>
+        <v>0.4752959999999988</v>
       </c>
       <c r="E3">
-        <v>0.4728409805834767</v>
+        <v>0.4728389431404009</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4653692108395329</v>
+        <v>0.4652913006894609</v>
       </c>
       <c r="H3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="I3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4430742400710007</v>
+        <v>0.4443697197086736</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>

--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -516,7 +516,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>0.5143399999999999</v>
+        <v>0.51434</v>
       </c>
       <c r="D2">
         <v>0.4959839999999996</v>
@@ -528,7 +528,7 @@
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064231917089714</v>
+        <v>0.5064231917089715</v>
       </c>
       <c r="H2">
         <v>0.5264302802913263</v>
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.4577039999999986</v>
+        <v>0.4577039999999984</v>
       </c>
       <c r="D3">
         <v>0.4752959999999988</v>

--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -516,31 +516,31 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>0.51434</v>
+        <v>0.5142079999999999</v>
       </c>
       <c r="D2">
-        <v>0.4959839999999996</v>
+        <v>0.4958199999999996</v>
       </c>
       <c r="E2">
-        <v>0.4965387457485618</v>
+        <v>0.4976068069845513</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5064231917089715</v>
+        <v>0.5062773903434608</v>
       </c>
       <c r="H2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="I2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5264302802913263</v>
+        <v>0.529566065934066</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -563,31 +563,31 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.4577039999999984</v>
+        <v>0.4576439999999986</v>
       </c>
       <c r="D3">
-        <v>0.4752959999999988</v>
+        <v>0.4753639999999988</v>
       </c>
       <c r="E3">
-        <v>0.4728389431404009</v>
+        <v>0.4714935259345234</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4652913006894609</v>
+        <v>0.4652865061515034</v>
       </c>
       <c r="H3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="I3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4443697197086736</v>
+        <v>0.441233934065934</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>

--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -516,31 +516,31 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>0.5142079999999999</v>
+        <v>0.5143840000000001</v>
       </c>
       <c r="D2">
-        <v>0.4958199999999996</v>
+        <v>0.4959679999999996</v>
       </c>
       <c r="E2">
-        <v>0.4976068069845513</v>
+        <v>0.4972024416993439</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.5062773903434608</v>
+        <v>0.506441314148639</v>
       </c>
       <c r="H2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="I2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.529566065934066</v>
+        <v>0.5280457815565729</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -563,31 +563,31 @@
         <v>25</v>
       </c>
       <c r="C3">
-        <v>0.4576439999999986</v>
+        <v>0.4577239999999985</v>
       </c>
       <c r="D3">
-        <v>0.4753639999999988</v>
+        <v>0.4752239999999988</v>
       </c>
       <c r="E3">
-        <v>0.4714935259345234</v>
+        <v>0.471947408691133</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4652865061515034</v>
+        <v>0.4652716217636178</v>
       </c>
       <c r="H3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="I3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.441233934065934</v>
+        <v>0.4427542184434272</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
